--- a/partner_import_helper/tests/res_partner_import_test.xlsx
+++ b/partner_import_helper/tests/res_partner_import_test.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="companies" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="73">
   <si>
     <t xml:space="preserve">company_ref</t>
   </si>
@@ -150,88 +150,97 @@
     <t xml:space="preserve">FRN001</t>
   </si>
   <si>
-    <t xml:space="preserve">ALUVAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR52948140546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 rue perriere LA MEMBROLLE SUR LONGUENEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONGUENEE EN ANJOU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+34 2 40 78 77 32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 68 49 89 60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arnaud.layec@akretion.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.akretion.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banque &amp; Assurance</t>
+    <t xml:space="preserve">Ma Société</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR00000000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'FR' ou 'Grande Bretagne'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 rue de la cité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma Ville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 40 01 01 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 01 01 01 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prenom.nom@email.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.company.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banque &amp; Assurance, Transports, Energies, …</t>
   </si>
   <si>
     <t xml:space="preserve">fr_FR</t>
   </si>
   <si>
+    <t xml:space="preserve"> Bâtiment,Energie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prénom NOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 rue de la cité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon Village</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 40 02 02 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 02 02 02 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 rue de la cité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ville3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 40 03 03 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 03 03 03 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">title_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directrice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 05 05 05 05</t>
+  </si>
+  <si>
     <t xml:space="preserve">Energie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul MICHEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monsieur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 allée des violettes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Chapelle sur Erdre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julie LEBRUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 chemin des embruns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">title_code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">function</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directrice adjointe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR7600000000000000000000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAAAFRPPXXX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ma Banque</t>
   </si>
 </sst>
 </file>
@@ -335,6 +344,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -345,10 +358,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -604,12 +613,13 @@
   <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="17.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="43.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.95"/>
@@ -636,133 +646,135 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="17.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="22.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="15.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="12.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="13.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="11.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="16.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="15.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="39" style="1" width="13.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="22.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="13.15"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16373" min="41" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16380" style="2" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>39</v>
       </c>
     </row>
@@ -780,7 +792,7 @@
         <v>43</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>44316952400120</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>44</v>
@@ -792,18 +804,18 @@
         <v>46</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>49770</v>
-      </c>
-      <c r="K2" s="3" t="s">
+        <v>11111</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="5" t="s">
         <v>50</v>
       </c>
       <c r="R2" s="1" t="s">
@@ -812,7 +824,7 @@
       <c r="S2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="4" t="s">
         <v>53</v>
       </c>
       <c r="U2" s="1" t="s">
@@ -828,42 +840,42 @@
         <v>57</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>44240</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC2" s="4" t="s">
+        <v>12333</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC2" s="5" t="s">
         <v>49</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AJ2" s="1" t="n">
-        <v>75018</v>
-      </c>
-      <c r="AK2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM2" s="4" t="s">
+        <v>15000</v>
+      </c>
+      <c r="AK2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AL2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM2" s="5" t="s">
         <v>49</v>
       </c>
       <c r="AN2" s="1" t="s">
@@ -872,10 +884,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" display="arnaud.layec@akretion.com"/>
-    <hyperlink ref="N2" r:id="rId2" display="https://www.akretion.com"/>
-    <hyperlink ref="AC2" r:id="rId3" display="arnaud.layec@akretion.com"/>
-    <hyperlink ref="AM2" r:id="rId4" display="arnaud.layec@akretion.com"/>
+    <hyperlink ref="M2" r:id="rId1" display="prenom.nom@email.com"/>
+    <hyperlink ref="N2" r:id="rId2" display="https://www.company.com"/>
+    <hyperlink ref="AM2" r:id="rId3" display="prenom.nom@email.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -892,118 +903,120 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1048576"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="16.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="17.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="22.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="17.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="5" width="22.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="15.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="5" width="12.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="5" width="11.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="16.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="5" width="15.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="5" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="16.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="2" width="17.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="22.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="17.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="2" width="22.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="12.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="11.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="16.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="15.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="22.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="12.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="C2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>75018</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="F2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="L2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>53</v>
+      <c r="O2" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1" display="arnaud.layec@akretion.com"/>
+    <hyperlink ref="M2" r:id="rId1" display="prenom.nom@email.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -1020,49 +1033,42 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="5" width="20.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="31.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="16.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="11.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="21.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="20.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="20.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="16.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>69</v>
-      </c>
     </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
